--- a/stock_validation.xlsx
+++ b/stock_validation.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -534,7 +534,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -544,9 +544,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -564,6 +561,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2560,7 +2561,7 @@
       </c>
     </row>
     <row r="35" spans="4:21" x14ac:dyDescent="0.45">
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E35">
